--- a/content/blurb_worklist_rbwr.xlsx
+++ b/content/blurb_worklist_rbwr.xlsx
@@ -4057,7 +4057,7 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Not expected to play for 49ers this year, not fantasy relevant</t>
+          <t>Not expected to play for 49ers this year, not fantasy relevant. If he does land somewhere, should not be ranked inside top 60.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
